--- a/templates/2027/mock/04_優異旅團獲獎名單.xlsx
+++ b/templates/2027/mock/04_優異旅團獲獎名單.xlsx
@@ -31,8 +31,11 @@
         <r>
           <t xml:space="preserve">必須 — 冇就唔成立
 型別：text
-例：港島第六旅
-同「支部」一齊做唯一鍵。寫法要同參加旅團表一致</t>
+例：港島第6旅
+同「支部」一齊做唯一鍵。寫法要同參加旅團表一致
+只准填「港島第1旅」咁嘅寫法：區名 ＋ 第 ＋ 阿拉伯數字 ＋ 旅。
+✓ 可以：港島第1旅、港島第263旅、港島第5海童軍旅
+✗ 唔好：港島第一旅（中文數字）、1（冇區名）、第1旅（冇區名）、港島1（冇「第」同「旅」）</t>
         </r>
       </text>
     </comment>
@@ -60,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="142">
   <si>
     <t>區</t>
   </si>
@@ -419,7 +422,13 @@
     <t xml:space="preserve">　2.</t>
   </si>
   <si>
-    <t>旅名要寫全（港島第六旅），唔好簡寫，唱名會照讀。</t>
+    <t>旅名只准填阿拉伯數字：港島第6旅。唔准填「港島第六旅」或者淨係「6」——2026 就係兩張表各有各寫法。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　3.</t>
+  </si>
+  <si>
+    <t>唱名要中文數字係司儀嘅事，系統會自動轉，唔使你喺度填中文。</t>
   </si>
   <si>
     <t>欄</t>
@@ -431,7 +440,7 @@
     <t>級別</t>
   </si>
   <si>
-    <t>型別</t>
+    <t>格式</t>
   </si>
   <si>
     <t>例子</t>
@@ -449,7 +458,13 @@
     <t>B</t>
   </si>
   <si>
-    <t>同「支部」一齊做唯一鍵。寫法要同參加旅團表一致</t>
+    <t>港島第1旅</t>
+  </si>
+  <si>
+    <t>港島第6旅</t>
+  </si>
+  <si>
+    <t>只准填「港島第1旅」咁嘅寫法：區名 ＋ 第 ＋ 阿拉伯數字 ＋ 旅。　✓港島第1旅／港島第263旅／港島第5海童軍旅　✗港島第一旅（中文數字）／1（冇區名）／第1旅（冇區名）／港島1（冇「第」同「旅」）　同「支部」一齊做唯一鍵。寫法要同參加旅團表一致</t>
   </si>
   <si>
     <t>C</t>
@@ -897,7 +912,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D190"/>
+  <dimension ref="A1:D688"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -932,2640 +947,3142 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="208" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="210" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="211" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="212" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="213" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="214" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="215" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="216" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="217" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="218" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="219" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="220" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="221" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="222" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="223" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="224" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="225" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="226" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="227" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="228" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="229" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="230" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="231" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="232" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="233" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="234" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="235" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="236" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="237" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="238" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="239" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="240" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="241" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="242" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="243" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="244" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="245" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="246" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="247" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="248" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="249" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="250" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="251" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="252" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="253" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="254" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="255" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="256" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="257" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="258" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="259" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="260" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="261" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="262" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="263" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="264" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="265" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="266" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="267" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="268" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="269" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="270" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="271" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="272" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="273" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="274" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="275" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="276" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="277" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="278" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="279" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="280" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="281" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="282" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="283" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="284" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="285" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="286" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="287" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="288" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="289" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="290" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="291" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="292" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="293" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="294" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="295" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="296" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="297" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="298" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="299" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="300" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="301" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="302" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="303" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="304" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="305" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="306" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="307" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="308" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="309" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="310" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="311" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="312" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="313" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="314" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="315" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="316" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="317" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="318" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="319" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="320" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="321" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="322" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="323" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="324" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="325" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="326" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="327" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="328" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="329" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="330" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="331" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="332" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="333" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="334" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="335" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="336" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="337" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="338" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="339" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="340" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="341" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="342" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="343" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="344" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="345" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="346" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="347" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="348" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="349" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="350" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="351" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="352" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="353" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="354" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="355" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="356" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="357" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="358" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="359" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="360" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="361" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="362" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="363" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="364" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="365" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="366" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="367" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="368" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="369" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="370" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="371" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="372" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="373" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="374" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="375" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="376" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="377" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="378" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="379" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="380" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="381" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="382" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="383" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="384" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="385" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="386" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="387" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="388" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="389" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="390" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="391" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="392" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="393" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="394" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="395" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="396" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="397" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="398" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="399" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="400" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="401" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="402" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="403" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="404" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="405" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="406" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="407" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="408" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="409" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="410" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="411" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="412" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="413" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="414" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="415" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="416" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="417" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="418" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="419" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="420" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="421" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="422" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="423" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="424" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="425" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="426" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="427" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="428" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="429" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="430" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="431" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="432" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="433" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="434" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="435" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="436" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="437" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="438" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="439" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="440" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="441" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="442" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="443" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="444" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="445" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="446" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="447" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="448" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="449" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="450" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="451" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="452" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="453" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="454" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="455" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="456" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="457" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="458" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="459" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="460" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="461" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="462" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="463" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="464" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="465" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="466" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="467" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="468" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="469" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="470" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="471" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="472" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="473" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="474" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="475" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="476" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="477" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="478" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="479" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="480" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="481" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="482" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="483" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="484" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="485" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="486" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="487" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="488" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="489" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="490" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="491" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="492" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="493" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="494" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="495" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="496" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="497" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="498" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="499" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="500" spans="2:2" x14ac:dyDescent="0.25"/>
+    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A501" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B501" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C501" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="D501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A502" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B502" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C502" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="D502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A503" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B503" t="s">
         <v>7</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C503" t="s">
         <v>12</v>
       </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="D503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A504" t="s">
         <v>6</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B504" t="s">
         <v>10</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C504" t="s">
         <v>13</v>
       </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="D504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B505" t="s">
         <v>7</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C505" t="s">
         <v>11</v>
       </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="D505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A506" t="s">
         <v>6</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B506" t="s">
         <v>14</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C506" t="s">
         <v>8</v>
       </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="D506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A507" t="s">
         <v>6</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B507" t="s">
         <v>7</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C507" t="s">
         <v>13</v>
       </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="D507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A508" t="s">
         <v>6</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B508" t="s">
         <v>14</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C508" t="s">
         <v>12</v>
       </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="D508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A509" t="s">
         <v>6</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B509" t="s">
         <v>7</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C509" t="s">
         <v>15</v>
       </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="D509" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A510" t="s">
         <v>6</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B510" t="s">
         <v>16</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C510" t="s">
         <v>12</v>
       </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="D510" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A511" t="s">
         <v>6</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B511" t="s">
         <v>17</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C511" t="s">
         <v>11</v>
       </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="D511" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A512" t="s">
         <v>6</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B512" t="s">
         <v>18</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C512" t="s">
         <v>11</v>
       </c>
-      <c r="D14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="D512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A513" t="s">
         <v>6</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B513" t="s">
         <v>19</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C513" t="s">
         <v>11</v>
       </c>
-      <c r="D15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="D513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A514" t="s">
         <v>6</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B514" t="s">
         <v>20</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C514" t="s">
         <v>12</v>
       </c>
-      <c r="D16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="D514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A515" t="s">
         <v>6</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B515" t="s">
         <v>19</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C515" t="s">
         <v>13</v>
       </c>
-      <c r="D17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="D515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A516" t="s">
         <v>6</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B516" t="s">
         <v>21</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C516" t="s">
         <v>12</v>
       </c>
-      <c r="D18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="D516" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A517" t="s">
         <v>6</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B517" t="s">
         <v>10</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C517" t="s">
         <v>8</v>
       </c>
-      <c r="D19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="D517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A518" t="s">
         <v>6</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B518" t="s">
         <v>22</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C518" t="s">
         <v>12</v>
       </c>
-      <c r="D20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="D518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A519" t="s">
         <v>6</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B519" t="s">
         <v>10</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C519" t="s">
         <v>12</v>
       </c>
-      <c r="D21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="D519" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A520" t="s">
         <v>23</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B520" t="s">
         <v>24</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C520" t="s">
         <v>8</v>
       </c>
-      <c r="D22" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="D520" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A521" t="s">
         <v>23</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B521" t="s">
         <v>25</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C521" t="s">
         <v>8</v>
       </c>
-      <c r="D23" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="D521" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A522" t="s">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B522" t="s">
         <v>24</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C522" t="s">
         <v>26</v>
       </c>
-      <c r="D24" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="D522" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A523" t="s">
         <v>23</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B523" t="s">
         <v>25</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C523" t="s">
         <v>12</v>
       </c>
-      <c r="D25" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="D523" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A524" t="s">
         <v>23</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B524" t="s">
         <v>24</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C524" t="s">
         <v>27</v>
       </c>
-      <c r="D26" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="D524" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A525" t="s">
         <v>23</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B525" t="s">
         <v>25</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C525" t="s">
         <v>11</v>
       </c>
-      <c r="D27" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="D525" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A526" t="s">
         <v>23</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B526" t="s">
         <v>24</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C526" t="s">
         <v>28</v>
       </c>
-      <c r="D28" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="D526" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A527" t="s">
         <v>23</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B527" t="s">
         <v>29</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C527" t="s">
         <v>30</v>
       </c>
-      <c r="D29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="D527" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A528" t="s">
         <v>23</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B528" t="s">
         <v>24</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C528" t="s">
         <v>31</v>
       </c>
-      <c r="D30" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="D528" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A529" t="s">
         <v>23</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B529" t="s">
         <v>29</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C529" t="s">
         <v>32</v>
       </c>
-      <c r="D31" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="D529" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A530" t="s">
         <v>23</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B530" t="s">
         <v>24</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C530" t="s">
         <v>33</v>
       </c>
-      <c r="D32" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="D530" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A531" t="s">
         <v>23</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B531" t="s">
         <v>29</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C531" t="s">
         <v>26</v>
       </c>
-      <c r="D33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="D531" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A532" t="s">
         <v>23</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B532" t="s">
         <v>24</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C532" t="s">
         <v>13</v>
       </c>
-      <c r="D34" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="D532" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A533" t="s">
         <v>23</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B533" t="s">
         <v>29</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C533" t="s">
         <v>27</v>
       </c>
-      <c r="D35" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="D533" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A534" t="s">
         <v>23</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B534" t="s">
         <v>24</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C534" t="s">
         <v>15</v>
       </c>
-      <c r="D36" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="D534" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A535" t="s">
         <v>23</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B535" t="s">
         <v>29</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C535" t="s">
         <v>13</v>
       </c>
-      <c r="D37" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="D535" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A536" t="s">
         <v>23</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B536" t="s">
         <v>34</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C536" t="s">
         <v>35</v>
       </c>
-      <c r="D38" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="D536" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A537" t="s">
         <v>23</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B537" t="s">
         <v>36</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C537" t="s">
         <v>11</v>
       </c>
-      <c r="D39" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="D537" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A538" t="s">
         <v>23</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B538" t="s">
         <v>34</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C538" t="s">
         <v>37</v>
       </c>
-      <c r="D40" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="D538" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A539" t="s">
         <v>23</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B539" t="s">
         <v>38</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C539" t="s">
         <v>11</v>
       </c>
-      <c r="D41" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="D539" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A540" t="s">
         <v>23</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B540" t="s">
         <v>39</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C540" t="s">
         <v>11</v>
       </c>
-      <c r="D42" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="D540" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A541" t="s">
         <v>23</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B541" t="s">
         <v>40</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C541" t="s">
         <v>30</v>
       </c>
-      <c r="D43" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="D541" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A542" t="s">
         <v>23</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B542" t="s">
         <v>39</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C542" t="s">
         <v>13</v>
       </c>
-      <c r="D44" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="D542" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A543" t="s">
         <v>23</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B543" t="s">
         <v>40</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C543" t="s">
         <v>32</v>
       </c>
-      <c r="D45" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="D543" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A544" t="s">
         <v>23</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B544" t="s">
         <v>41</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C544" t="s">
         <v>11</v>
       </c>
-      <c r="D46" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="D544" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A545" t="s">
         <v>23</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B545" t="s">
         <v>40</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C545" t="s">
         <v>42</v>
       </c>
-      <c r="D47" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="D545" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A546" t="s">
         <v>23</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B546" t="s">
         <v>43</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C546" t="s">
         <v>12</v>
       </c>
-      <c r="D48" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="D546" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A547" t="s">
         <v>44</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B547" t="s">
         <v>45</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C547" t="s">
         <v>11</v>
       </c>
-      <c r="D49" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="D547" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A548" t="s">
         <v>44</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B548" t="s">
         <v>46</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C548" t="s">
         <v>15</v>
       </c>
-      <c r="D50" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="D548" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A549" t="s">
         <v>44</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B549" t="s">
         <v>47</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C549" t="s">
         <v>12</v>
       </c>
-      <c r="D51" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="D549" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A550" t="s">
         <v>44</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B550" t="s">
         <v>48</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C550" t="s">
         <v>30</v>
       </c>
-      <c r="D52" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="D550" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A551" t="s">
         <v>44</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B551" t="s">
         <v>47</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C551" t="s">
         <v>11</v>
       </c>
-      <c r="D53" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="D551" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A552" t="s">
         <v>44</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B552" t="s">
         <v>48</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C552" t="s">
         <v>32</v>
       </c>
-      <c r="D54" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="D552" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A553" t="s">
         <v>44</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B553" t="s">
         <v>47</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C553" t="s">
         <v>13</v>
       </c>
-      <c r="D55" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="D553" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A554" t="s">
         <v>44</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B554" t="s">
         <v>48</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C554" t="s">
         <v>26</v>
       </c>
-      <c r="D56" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="D554" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A555" t="s">
         <v>44</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B555" t="s">
         <v>49</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C555" t="s">
         <v>12</v>
       </c>
-      <c r="D57" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="D555" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A556" t="s">
         <v>44</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B556" t="s">
         <v>48</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C556" t="s">
         <v>27</v>
       </c>
-      <c r="D58" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="D556" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A557" t="s">
         <v>44</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B557" t="s">
         <v>46</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C557" t="s">
         <v>11</v>
       </c>
-      <c r="D59" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="D557" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A558" t="s">
         <v>44</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B558" t="s">
         <v>50</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C558" t="s">
         <v>12</v>
       </c>
-      <c r="D60" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="D558" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A559" t="s">
         <v>44</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B559" t="s">
         <v>46</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C559" t="s">
         <v>13</v>
       </c>
-      <c r="D61" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="D559" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A560" t="s">
         <v>44</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B560" t="s">
         <v>51</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C560" t="s">
         <v>8</v>
       </c>
-      <c r="D62" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="D560" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A561" t="s">
         <v>52</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B561" t="s">
         <v>53</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C561" t="s">
         <v>11</v>
       </c>
-      <c r="D63" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="D561" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A562" t="s">
         <v>52</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B562" t="s">
         <v>54</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C562" t="s">
         <v>12</v>
       </c>
-      <c r="D64" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="D562" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A563" t="s">
         <v>52</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B563" t="s">
         <v>53</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C563" t="s">
         <v>13</v>
       </c>
-      <c r="D65" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="D563" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A564" t="s">
         <v>52</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B564" t="s">
         <v>55</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C564" t="s">
         <v>8</v>
       </c>
-      <c r="D66" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="D564" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A565" t="s">
         <v>52</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B565" t="s">
         <v>56</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C565" t="s">
         <v>8</v>
       </c>
-      <c r="D67" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+      <c r="D565" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A566" t="s">
         <v>52</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B566" t="s">
         <v>55</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C566" t="s">
         <v>12</v>
       </c>
-      <c r="D68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="D566" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A567" t="s">
         <v>52</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B567" t="s">
         <v>56</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C567" t="s">
         <v>12</v>
       </c>
-      <c r="D69" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="D567" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A568" t="s">
         <v>52</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B568" t="s">
         <v>55</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C568" t="s">
         <v>11</v>
       </c>
-      <c r="D70" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="D568" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A569" t="s">
         <v>52</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B569" t="s">
         <v>56</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C569" t="s">
         <v>11</v>
       </c>
-      <c r="D71" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="D569" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A570" t="s">
         <v>52</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B570" t="s">
         <v>55</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C570" t="s">
         <v>13</v>
       </c>
-      <c r="D72" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="D570" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A571" t="s">
         <v>52</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B571" t="s">
         <v>56</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C571" t="s">
         <v>13</v>
       </c>
-      <c r="D73" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="D571" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A572" t="s">
         <v>52</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B572" t="s">
         <v>57</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C572" t="s">
         <v>12</v>
       </c>
-      <c r="D74" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+      <c r="D572" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A573" t="s">
         <v>52</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B573" t="s">
         <v>56</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C573" t="s">
         <v>15</v>
       </c>
-      <c r="D75" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="D573" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A574" t="s">
         <v>52</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B574" t="s">
         <v>57</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C574" t="s">
         <v>11</v>
       </c>
-      <c r="D76" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="D574" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A575" t="s">
         <v>52</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B575" t="s">
         <v>58</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C575" t="s">
         <v>12</v>
       </c>
-      <c r="D77" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="D575" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A576" t="s">
         <v>52</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B576" t="s">
         <v>57</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C576" t="s">
         <v>13</v>
       </c>
-      <c r="D78" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+      <c r="D576" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A577" t="s">
         <v>52</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B577" t="s">
         <v>58</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C577" t="s">
         <v>11</v>
       </c>
-      <c r="D79" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+      <c r="D577" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A578" t="s">
         <v>52</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B578" t="s">
         <v>59</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C578" t="s">
         <v>12</v>
       </c>
-      <c r="D80" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="D578" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A579" t="s">
         <v>52</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B579" t="s">
         <v>58</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C579" t="s">
         <v>13</v>
       </c>
-      <c r="D81" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="D579" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="580" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A580" t="s">
         <v>52</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B580" t="s">
         <v>60</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C580" t="s">
         <v>12</v>
       </c>
-      <c r="D82" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="D580" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A581" t="s">
         <v>52</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B581" t="s">
         <v>61</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C581" t="s">
         <v>13</v>
       </c>
-      <c r="D83" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="D581" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A582" t="s">
         <v>52</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B582" t="s">
         <v>62</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C582" t="s">
         <v>12</v>
       </c>
-      <c r="D84" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+      <c r="D582" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A583" t="s">
         <v>52</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B583" t="s">
         <v>54</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C583" t="s">
         <v>8</v>
       </c>
-      <c r="D85" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+      <c r="D583" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A584" t="s">
         <v>52</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B584" t="s">
         <v>63</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C584" t="s">
         <v>15</v>
       </c>
-      <c r="D86" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="D584" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A585" t="s">
         <v>64</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B585" t="s">
         <v>65</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C585" t="s">
         <v>11</v>
       </c>
-      <c r="D87" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="D585" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="586" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A586" t="s">
         <v>64</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B586" t="s">
         <v>66</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C586" t="s">
         <v>12</v>
       </c>
-      <c r="D88" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+      <c r="D586" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="587" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A587" t="s">
         <v>64</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B587" t="s">
         <v>67</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C587" t="s">
         <v>12</v>
       </c>
-      <c r="D89" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="D587" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="588" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A588" t="s">
         <v>64</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B588" t="s">
         <v>66</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C588" t="s">
         <v>11</v>
       </c>
-      <c r="D90" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+      <c r="D588" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A589" t="s">
         <v>64</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B589" t="s">
         <v>67</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C589" t="s">
         <v>11</v>
       </c>
-      <c r="D91" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+      <c r="D589" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A590" t="s">
         <v>64</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B590" t="s">
         <v>68</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C590" t="s">
         <v>26</v>
       </c>
-      <c r="D92" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+      <c r="D590" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A591" t="s">
         <v>64</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B591" t="s">
         <v>67</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C591" t="s">
         <v>13</v>
       </c>
-      <c r="D93" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+      <c r="D591" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A592" t="s">
         <v>64</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B592" t="s">
         <v>68</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C592" t="s">
         <v>27</v>
       </c>
-      <c r="D94" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
+      <c r="D592" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A593" t="s">
         <v>64</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B593" t="s">
         <v>69</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C593" t="s">
         <v>13</v>
       </c>
-      <c r="D95" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+      <c r="D593" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="594" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A594" t="s">
         <v>64</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B594" t="s">
         <v>68</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C594" t="s">
         <v>11</v>
       </c>
-      <c r="D96" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+      <c r="D594" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A595" t="s">
         <v>64</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B595" t="s">
         <v>69</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C595" t="s">
         <v>70</v>
       </c>
-      <c r="D97" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+      <c r="D595" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A596" t="s">
         <v>64</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B596" t="s">
         <v>71</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C596" t="s">
         <v>12</v>
       </c>
-      <c r="D98" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+      <c r="D596" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A597" t="s">
         <v>64</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B597" t="s">
         <v>69</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C597" t="s">
         <v>15</v>
       </c>
-      <c r="D99" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
+      <c r="D597" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A598" t="s">
         <v>64</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B598" t="s">
         <v>71</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C598" t="s">
         <v>11</v>
       </c>
-      <c r="D100" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+      <c r="D598" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A599" t="s">
         <v>64</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B599" t="s">
         <v>69</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C599" t="s">
         <v>72</v>
       </c>
-      <c r="D101" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
+      <c r="D599" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A600" t="s">
         <v>64</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B600" t="s">
         <v>73</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C600" t="s">
         <v>11</v>
       </c>
-      <c r="D102" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+      <c r="D600" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A601" t="s">
         <v>64</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B601" t="s">
         <v>66</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C601" t="s">
         <v>8</v>
       </c>
-      <c r="D103" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+      <c r="D601" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A602" t="s">
         <v>74</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B602" t="s">
         <v>75</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C602" t="s">
         <v>8</v>
       </c>
-      <c r="D104" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
+      <c r="D602" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A603" t="s">
         <v>74</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B603" t="s">
         <v>76</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C603" t="s">
         <v>11</v>
       </c>
-      <c r="D105" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
+      <c r="D603" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A604" t="s">
         <v>74</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B604" t="s">
         <v>75</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C604" t="s">
         <v>26</v>
       </c>
-      <c r="D106" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+      <c r="D604" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="605" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A605" t="s">
         <v>74</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B605" t="s">
         <v>76</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C605" t="s">
         <v>13</v>
       </c>
-      <c r="D107" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+      <c r="D605" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A606" t="s">
         <v>74</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B606" t="s">
         <v>75</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C606" t="s">
         <v>27</v>
       </c>
-      <c r="D108" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
+      <c r="D606" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="607" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A607" t="s">
         <v>74</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B607" t="s">
         <v>77</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C607" t="s">
         <v>30</v>
       </c>
-      <c r="D109" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+      <c r="D607" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A608" t="s">
         <v>74</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B608" t="s">
         <v>75</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C608" t="s">
         <v>11</v>
       </c>
-      <c r="D110" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
+      <c r="D608" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="609" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A609" t="s">
         <v>74</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B609" t="s">
         <v>77</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C609" t="s">
         <v>32</v>
       </c>
-      <c r="D111" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
+      <c r="D609" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="610" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A610" t="s">
         <v>74</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B610" t="s">
         <v>75</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C610" t="s">
         <v>78</v>
       </c>
-      <c r="D112" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
+      <c r="D610" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A611" t="s">
         <v>74</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B611" t="s">
         <v>77</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C611" t="s">
         <v>26</v>
       </c>
-      <c r="D113" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
+      <c r="D611" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A612" t="s">
         <v>74</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B612" t="s">
         <v>75</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C612" t="s">
         <v>13</v>
       </c>
-      <c r="D114" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
+      <c r="D612" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="613" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A613" t="s">
         <v>74</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B613" t="s">
         <v>77</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C613" t="s">
         <v>27</v>
       </c>
-      <c r="D115" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
+      <c r="D613" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="614" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A614" t="s">
         <v>74</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B614" t="s">
         <v>75</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C614" t="s">
         <v>15</v>
       </c>
-      <c r="D116" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
+      <c r="D614" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="615" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A615" t="s">
         <v>74</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B615" t="s">
         <v>77</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C615" t="s">
         <v>11</v>
       </c>
-      <c r="D117" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
+      <c r="D615" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A616" t="s">
         <v>74</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B616" t="s">
         <v>79</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C616" t="s">
         <v>12</v>
       </c>
-      <c r="D118" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
+      <c r="D616" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="617" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A617" t="s">
         <v>74</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B617" t="s">
         <v>77</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C617" t="s">
         <v>78</v>
       </c>
-      <c r="D119" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
+      <c r="D617" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A618" t="s">
         <v>74</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B618" t="s">
         <v>79</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C618" t="s">
         <v>11</v>
       </c>
-      <c r="D120" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
+      <c r="D618" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A619" t="s">
         <v>74</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B619" t="s">
         <v>77</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C619" t="s">
         <v>13</v>
       </c>
-      <c r="D121" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
+      <c r="D619" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="620" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A620" t="s">
         <v>74</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B620" t="s">
         <v>80</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C620" t="s">
         <v>30</v>
       </c>
-      <c r="D122" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
+      <c r="D620" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A621" t="s">
         <v>74</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B621" t="s">
         <v>77</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C621" t="s">
         <v>70</v>
       </c>
-      <c r="D123" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
+      <c r="D621" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A622" t="s">
         <v>74</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B622" t="s">
         <v>80</v>
       </c>
-      <c r="C124" t="s">
+      <c r="C622" t="s">
         <v>32</v>
       </c>
-      <c r="D124" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
+      <c r="D622" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="623" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A623" t="s">
         <v>74</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B623" t="s">
         <v>77</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C623" t="s">
         <v>15</v>
       </c>
-      <c r="D125" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
+      <c r="D623" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="624" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A624" t="s">
         <v>74</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B624" t="s">
         <v>80</v>
       </c>
-      <c r="C126" t="s">
+      <c r="C624" t="s">
         <v>26</v>
       </c>
-      <c r="D126" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
+      <c r="D624" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="625" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A625" t="s">
         <v>74</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B625" t="s">
         <v>81</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C625" t="s">
         <v>30</v>
       </c>
-      <c r="D127" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
+      <c r="D625" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="626" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A626" t="s">
         <v>74</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B626" t="s">
         <v>80</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C626" t="s">
         <v>27</v>
       </c>
-      <c r="D128" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
+      <c r="D626" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="627" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A627" t="s">
         <v>74</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B627" t="s">
         <v>81</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C627" t="s">
         <v>32</v>
       </c>
-      <c r="D129" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
+      <c r="D627" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="628" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A628" t="s">
         <v>74</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B628" t="s">
         <v>80</v>
       </c>
-      <c r="C130" t="s">
+      <c r="C628" t="s">
         <v>35</v>
       </c>
-      <c r="D130" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
+      <c r="D628" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="629" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A629" t="s">
         <v>74</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B629" t="s">
         <v>81</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C629" t="s">
         <v>26</v>
       </c>
-      <c r="D131" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
+      <c r="D629" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="630" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A630" t="s">
         <v>74</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B630" t="s">
         <v>82</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C630" t="s">
         <v>12</v>
       </c>
-      <c r="D132" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
+      <c r="D630" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="631" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A631" t="s">
         <v>74</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B631" t="s">
         <v>81</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C631" t="s">
         <v>27</v>
       </c>
-      <c r="D133" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
+      <c r="D631" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="632" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A632" t="s">
         <v>74</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B632" t="s">
         <v>82</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C632" t="s">
         <v>11</v>
       </c>
-      <c r="D134" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
+      <c r="D632" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="633" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A633" t="s">
         <v>74</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B633" t="s">
         <v>83</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C633" t="s">
         <v>8</v>
       </c>
-      <c r="D135" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
+      <c r="D633" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="634" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A634" t="s">
         <v>74</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B634" t="s">
         <v>84</v>
       </c>
-      <c r="C136" t="s">
+      <c r="C634" t="s">
         <v>13</v>
       </c>
-      <c r="D136" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
+      <c r="D634" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="635" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A635" t="s">
         <v>74</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B635" t="s">
         <v>85</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C635" t="s">
         <v>12</v>
       </c>
-      <c r="D137" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>86</v>
-      </c>
-      <c r="B138" t="s">
+      <c r="D635" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="636" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A636" t="s">
+        <v>86</v>
+      </c>
+      <c r="B636" t="s">
         <v>87</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C636" t="s">
         <v>12</v>
       </c>
-      <c r="D138" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>86</v>
-      </c>
-      <c r="B139" t="s">
+      <c r="D636" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="637" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A637" t="s">
+        <v>86</v>
+      </c>
+      <c r="B637" t="s">
         <v>88</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C637" t="s">
         <v>27</v>
       </c>
-      <c r="D139" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>86</v>
-      </c>
-      <c r="B140" t="s">
+      <c r="D637" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="638" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A638" t="s">
+        <v>86</v>
+      </c>
+      <c r="B638" t="s">
         <v>87</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C638" t="s">
         <v>35</v>
       </c>
-      <c r="D140" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>86</v>
-      </c>
-      <c r="B141" t="s">
+      <c r="D638" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="639" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A639" t="s">
+        <v>86</v>
+      </c>
+      <c r="B639" t="s">
         <v>88</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C639" t="s">
         <v>11</v>
       </c>
-      <c r="D141" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>86</v>
-      </c>
-      <c r="B142" t="s">
+      <c r="D639" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="640" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A640" t="s">
+        <v>86</v>
+      </c>
+      <c r="B640" t="s">
         <v>89</v>
       </c>
-      <c r="C142" t="s">
+      <c r="C640" t="s">
         <v>11</v>
       </c>
-      <c r="D142" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>86</v>
-      </c>
-      <c r="B143" t="s">
+      <c r="D640" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="641" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A641" t="s">
+        <v>86</v>
+      </c>
+      <c r="B641" t="s">
         <v>88</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C641" t="s">
         <v>13</v>
       </c>
-      <c r="D143" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>86</v>
-      </c>
-      <c r="B144" t="s">
+      <c r="D641" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="642" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A642" t="s">
+        <v>86</v>
+      </c>
+      <c r="B642" t="s">
         <v>89</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C642" t="s">
         <v>13</v>
       </c>
-      <c r="D144" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>86</v>
-      </c>
-      <c r="B145" t="s">
+      <c r="D642" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="643" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A643" t="s">
+        <v>86</v>
+      </c>
+      <c r="B643" t="s">
         <v>88</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C643" t="s">
         <v>15</v>
       </c>
-      <c r="D145" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>86</v>
-      </c>
-      <c r="B146" t="s">
+      <c r="D643" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="644" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A644" t="s">
+        <v>86</v>
+      </c>
+      <c r="B644" t="s">
         <v>90</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C644" t="s">
         <v>8</v>
       </c>
-      <c r="D146" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>86</v>
-      </c>
-      <c r="B147" t="s">
+      <c r="D644" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="645" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A645" t="s">
+        <v>86</v>
+      </c>
+      <c r="B645" t="s">
         <v>91</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C645" t="s">
         <v>30</v>
       </c>
-      <c r="D147" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>86</v>
-      </c>
-      <c r="B148" t="s">
+      <c r="D645" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="646" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A646" t="s">
+        <v>86</v>
+      </c>
+      <c r="B646" t="s">
         <v>90</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C646" t="s">
         <v>26</v>
       </c>
-      <c r="D148" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>86</v>
-      </c>
-      <c r="B149" t="s">
+      <c r="D646" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="647" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A647" t="s">
+        <v>86</v>
+      </c>
+      <c r="B647" t="s">
         <v>91</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C647" t="s">
         <v>32</v>
       </c>
-      <c r="D149" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>86</v>
-      </c>
-      <c r="B150" t="s">
+      <c r="D647" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="648" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A648" t="s">
+        <v>86</v>
+      </c>
+      <c r="B648" t="s">
         <v>90</v>
       </c>
-      <c r="C150" t="s">
+      <c r="C648" t="s">
         <v>27</v>
       </c>
-      <c r="D150" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>86</v>
-      </c>
-      <c r="B151" t="s">
+      <c r="D648" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A649" t="s">
+        <v>86</v>
+      </c>
+      <c r="B649" t="s">
         <v>91</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C649" t="s">
         <v>42</v>
       </c>
-      <c r="D151" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
-        <v>86</v>
-      </c>
-      <c r="B152" t="s">
+      <c r="D649" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A650" t="s">
+        <v>86</v>
+      </c>
+      <c r="B650" t="s">
         <v>90</v>
       </c>
-      <c r="C152" t="s">
+      <c r="C650" t="s">
         <v>11</v>
       </c>
-      <c r="D152" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>86</v>
-      </c>
-      <c r="B153" t="s">
+      <c r="D650" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="651" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A651" t="s">
+        <v>86</v>
+      </c>
+      <c r="B651" t="s">
         <v>91</v>
       </c>
-      <c r="C153" t="s">
+      <c r="C651" t="s">
         <v>92</v>
       </c>
-      <c r="D153" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>86</v>
-      </c>
-      <c r="B154" t="s">
+      <c r="D651" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A652" t="s">
+        <v>86</v>
+      </c>
+      <c r="B652" t="s">
         <v>90</v>
       </c>
-      <c r="C154" t="s">
+      <c r="C652" t="s">
         <v>13</v>
       </c>
-      <c r="D154" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>86</v>
-      </c>
-      <c r="B155" t="s">
+      <c r="D652" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A653" t="s">
+        <v>86</v>
+      </c>
+      <c r="B653" t="s">
         <v>91</v>
       </c>
-      <c r="C155" t="s">
+      <c r="C653" t="s">
         <v>26</v>
       </c>
-      <c r="D155" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>86</v>
-      </c>
-      <c r="B156" t="s">
+      <c r="D653" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="654" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A654" t="s">
+        <v>86</v>
+      </c>
+      <c r="B654" t="s">
         <v>90</v>
       </c>
-      <c r="C156" t="s">
+      <c r="C654" t="s">
         <v>15</v>
       </c>
-      <c r="D156" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>86</v>
-      </c>
-      <c r="B157" t="s">
+      <c r="D654" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A655" t="s">
+        <v>86</v>
+      </c>
+      <c r="B655" t="s">
         <v>91</v>
       </c>
-      <c r="C157" t="s">
+      <c r="C655" t="s">
         <v>27</v>
       </c>
-      <c r="D157" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>86</v>
-      </c>
-      <c r="B158" t="s">
+      <c r="D655" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A656" t="s">
+        <v>86</v>
+      </c>
+      <c r="B656" t="s">
         <v>93</v>
       </c>
-      <c r="C158" t="s">
+      <c r="C656" t="s">
         <v>12</v>
       </c>
-      <c r="D158" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
-        <v>86</v>
-      </c>
-      <c r="B159" t="s">
+      <c r="D656" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="657" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A657" t="s">
+        <v>86</v>
+      </c>
+      <c r="B657" t="s">
         <v>94</v>
       </c>
-      <c r="C159" t="s">
+      <c r="C657" t="s">
         <v>12</v>
       </c>
-      <c r="D159" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
-        <v>86</v>
-      </c>
-      <c r="B160" t="s">
+      <c r="D657" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="658" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A658" t="s">
+        <v>86</v>
+      </c>
+      <c r="B658" t="s">
         <v>93</v>
       </c>
-      <c r="C160" t="s">
+      <c r="C658" t="s">
         <v>11</v>
       </c>
-      <c r="D160" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
-        <v>86</v>
-      </c>
-      <c r="B161" t="s">
+      <c r="D658" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="659" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A659" t="s">
+        <v>86</v>
+      </c>
+      <c r="B659" t="s">
         <v>95</v>
       </c>
-      <c r="C161" t="s">
+      <c r="C659" t="s">
         <v>11</v>
       </c>
-      <c r="D161" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
-        <v>86</v>
-      </c>
-      <c r="B162" t="s">
+      <c r="D659" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="660" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A660" t="s">
+        <v>86</v>
+      </c>
+      <c r="B660" t="s">
         <v>93</v>
       </c>
-      <c r="C162" t="s">
+      <c r="C660" t="s">
         <v>37</v>
       </c>
-      <c r="D162" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>86</v>
-      </c>
-      <c r="B163" t="s">
+      <c r="D660" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="661" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A661" t="s">
+        <v>86</v>
+      </c>
+      <c r="B661" t="s">
         <v>95</v>
       </c>
-      <c r="C163" t="s">
+      <c r="C661" t="s">
         <v>96</v>
       </c>
-      <c r="D163" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>86</v>
-      </c>
-      <c r="B164" t="s">
+      <c r="D661" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="662" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A662" t="s">
+        <v>86</v>
+      </c>
+      <c r="B662" t="s">
         <v>93</v>
       </c>
-      <c r="C164" t="s">
+      <c r="C662" t="s">
         <v>15</v>
       </c>
-      <c r="D164" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>86</v>
-      </c>
-      <c r="B165" t="s">
+      <c r="D662" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="663" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A663" t="s">
+        <v>86</v>
+      </c>
+      <c r="B663" t="s">
         <v>95</v>
       </c>
-      <c r="C165" t="s">
+      <c r="C663" t="s">
         <v>97</v>
       </c>
-      <c r="D165" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
-        <v>86</v>
-      </c>
-      <c r="B166" t="s">
+      <c r="D663" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="664" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A664" t="s">
+        <v>86</v>
+      </c>
+      <c r="B664" t="s">
         <v>98</v>
       </c>
-      <c r="C166" t="s">
+      <c r="C664" t="s">
         <v>8</v>
       </c>
-      <c r="D166" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>86</v>
-      </c>
-      <c r="B167" t="s">
+      <c r="D664" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="665" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A665" t="s">
+        <v>86</v>
+      </c>
+      <c r="B665" t="s">
         <v>95</v>
       </c>
-      <c r="C167" t="s">
+      <c r="C665" t="s">
         <v>15</v>
       </c>
-      <c r="D167" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>86</v>
-      </c>
-      <c r="B168" t="s">
+      <c r="D665" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A666" t="s">
+        <v>86</v>
+      </c>
+      <c r="B666" t="s">
         <v>98</v>
       </c>
-      <c r="C168" t="s">
+      <c r="C666" t="s">
         <v>12</v>
       </c>
-      <c r="D168" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>86</v>
-      </c>
-      <c r="B169" t="s">
+      <c r="D666" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="667" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A667" t="s">
+        <v>86</v>
+      </c>
+      <c r="B667" t="s">
         <v>99</v>
       </c>
-      <c r="C169" t="s">
+      <c r="C667" t="s">
         <v>8</v>
       </c>
-      <c r="D169" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
-        <v>86</v>
-      </c>
-      <c r="B170" t="s">
+      <c r="D667" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="668" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A668" t="s">
+        <v>86</v>
+      </c>
+      <c r="B668" t="s">
         <v>98</v>
       </c>
-      <c r="C170" t="s">
+      <c r="C668" t="s">
         <v>13</v>
       </c>
-      <c r="D170" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>86</v>
-      </c>
-      <c r="B171" t="s">
+      <c r="D668" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="669" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A669" t="s">
+        <v>86</v>
+      </c>
+      <c r="B669" t="s">
         <v>99</v>
       </c>
-      <c r="C171" t="s">
+      <c r="C669" t="s">
         <v>26</v>
       </c>
-      <c r="D171" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>86</v>
-      </c>
-      <c r="B172" t="s">
+      <c r="D669" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="670" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A670" t="s">
+        <v>86</v>
+      </c>
+      <c r="B670" t="s">
         <v>98</v>
       </c>
-      <c r="C172" t="s">
+      <c r="C670" t="s">
         <v>15</v>
       </c>
-      <c r="D172" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
-        <v>86</v>
-      </c>
-      <c r="B173" t="s">
+      <c r="D670" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="671" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A671" t="s">
+        <v>86</v>
+      </c>
+      <c r="B671" t="s">
         <v>99</v>
       </c>
-      <c r="C173" t="s">
+      <c r="C671" t="s">
         <v>27</v>
       </c>
-      <c r="D173" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>86</v>
-      </c>
-      <c r="B174" t="s">
+      <c r="D671" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="672" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A672" t="s">
+        <v>86</v>
+      </c>
+      <c r="B672" t="s">
         <v>100</v>
       </c>
-      <c r="C174" t="s">
+      <c r="C672" t="s">
         <v>11</v>
       </c>
-      <c r="D174" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>86</v>
-      </c>
-      <c r="B175" t="s">
+      <c r="D672" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="673" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A673" t="s">
+        <v>86</v>
+      </c>
+      <c r="B673" t="s">
         <v>99</v>
       </c>
-      <c r="C175" t="s">
+      <c r="C673" t="s">
         <v>11</v>
       </c>
-      <c r="D175" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>86</v>
-      </c>
-      <c r="B176" t="s">
+      <c r="D673" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="674" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A674" t="s">
+        <v>86</v>
+      </c>
+      <c r="B674" t="s">
         <v>100</v>
       </c>
-      <c r="C176" t="s">
+      <c r="C674" t="s">
         <v>13</v>
       </c>
-      <c r="D176" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
-        <v>86</v>
-      </c>
-      <c r="B177" t="s">
+      <c r="D674" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="675" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A675" t="s">
+        <v>86</v>
+      </c>
+      <c r="B675" t="s">
         <v>99</v>
       </c>
-      <c r="C177" t="s">
+      <c r="C675" t="s">
         <v>13</v>
       </c>
-      <c r="D177" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
-        <v>86</v>
-      </c>
-      <c r="B178" t="s">
+      <c r="D675" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="676" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A676" t="s">
+        <v>86</v>
+      </c>
+      <c r="B676" t="s">
         <v>100</v>
       </c>
-      <c r="C178" t="s">
+      <c r="C676" t="s">
         <v>15</v>
       </c>
-      <c r="D178" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
-        <v>86</v>
-      </c>
-      <c r="B179" t="s">
+      <c r="D676" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="677" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A677" t="s">
+        <v>86</v>
+      </c>
+      <c r="B677" t="s">
         <v>99</v>
       </c>
-      <c r="C179" t="s">
+      <c r="C677" t="s">
         <v>15</v>
       </c>
-      <c r="D179" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
-        <v>86</v>
-      </c>
-      <c r="B180" t="s">
+      <c r="D677" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="678" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A678" t="s">
+        <v>86</v>
+      </c>
+      <c r="B678" t="s">
         <v>101</v>
       </c>
-      <c r="C180" t="s">
+      <c r="C678" t="s">
         <v>11</v>
       </c>
-      <c r="D180" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>86</v>
-      </c>
-      <c r="B181" t="s">
+      <c r="D678" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="679" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A679" t="s">
+        <v>86</v>
+      </c>
+      <c r="B679" t="s">
         <v>102</v>
       </c>
-      <c r="C181" t="s">
+      <c r="C679" t="s">
         <v>30</v>
       </c>
-      <c r="D181" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
-        <v>86</v>
-      </c>
-      <c r="B182" t="s">
+      <c r="D679" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="680" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A680" t="s">
+        <v>86</v>
+      </c>
+      <c r="B680" t="s">
         <v>101</v>
       </c>
-      <c r="C182" t="s">
+      <c r="C680" t="s">
         <v>13</v>
       </c>
-      <c r="D182" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>86</v>
-      </c>
-      <c r="B183" t="s">
+      <c r="D680" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="681" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A681" t="s">
+        <v>86</v>
+      </c>
+      <c r="B681" t="s">
         <v>102</v>
       </c>
-      <c r="C183" t="s">
+      <c r="C681" t="s">
         <v>32</v>
       </c>
-      <c r="D183" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>86</v>
-      </c>
-      <c r="B184" t="s">
+      <c r="D681" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="682" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A682" t="s">
+        <v>86</v>
+      </c>
+      <c r="B682" t="s">
         <v>103</v>
       </c>
-      <c r="C184" t="s">
+      <c r="C682" t="s">
         <v>12</v>
       </c>
-      <c r="D184" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>86</v>
-      </c>
-      <c r="B185" t="s">
+      <c r="D682" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="683" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A683" t="s">
+        <v>86</v>
+      </c>
+      <c r="B683" t="s">
         <v>104</v>
       </c>
-      <c r="C185" t="s">
+      <c r="C683" t="s">
         <v>8</v>
       </c>
-      <c r="D185" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>86</v>
-      </c>
-      <c r="B186" t="s">
+      <c r="D683" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="684" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A684" t="s">
+        <v>86</v>
+      </c>
+      <c r="B684" t="s">
         <v>88</v>
       </c>
-      <c r="C186" t="s">
+      <c r="C684" t="s">
         <v>30</v>
       </c>
-      <c r="D186" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>86</v>
-      </c>
-      <c r="B187" t="s">
+      <c r="D684" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="685" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A685" t="s">
+        <v>86</v>
+      </c>
+      <c r="B685" t="s">
         <v>105</v>
       </c>
-      <c r="C187" t="s">
+      <c r="C685" t="s">
         <v>12</v>
       </c>
-      <c r="D187" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
-        <v>86</v>
-      </c>
-      <c r="B188" t="s">
+      <c r="D685" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="686" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A686" t="s">
+        <v>86</v>
+      </c>
+      <c r="B686" t="s">
         <v>88</v>
       </c>
-      <c r="C188" t="s">
+      <c r="C686" t="s">
         <v>32</v>
       </c>
-      <c r="D188" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>86</v>
-      </c>
-      <c r="B189" t="s">
+      <c r="D686" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="687" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A687" t="s">
+        <v>86</v>
+      </c>
+      <c r="B687" t="s">
         <v>106</v>
       </c>
-      <c r="C189" t="s">
+      <c r="C687" t="s">
         <v>8</v>
       </c>
-      <c r="D189" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
-        <v>86</v>
-      </c>
-      <c r="B190" t="s">
+      <c r="D687" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="688" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A688" t="s">
+        <v>86</v>
+      </c>
+      <c r="B688" t="s">
         <v>88</v>
       </c>
-      <c r="C190" t="s">
+      <c r="C688" t="s">
         <v>26</v>
       </c>
-      <c r="D190" t="s">
+      <c r="D688" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>
+  <dataValidations count="2">
+    <dataValidation showInputMessage="1" promptTitle="旅團名稱　格式" prompt="只准填「港島第1旅」咁嘅寫法：區名 ＋ 第 ＋ 阿拉伯數字 ＋ 旅。  ✓ 可以：港島第1旅、港島第263旅、港島第5海童軍旅 ✗ 唔好：港島第一旅（中文數字）、1（冇區名）、第1旅（冇區名）、港島1（冇「第」同「旅」）" sqref="B10:B500"/>
+    <dataValidation showInputMessage="1" promptTitle="旅團名稱　格式" prompt="只准填「港島第1旅」咁嘅寫法：區名 ＋ 第 ＋ 阿拉伯數字 ＋ 旅。  ✓ 可以：港島第1旅、港島第263旅、港島第5海童軍旅 ✗ 唔好：港島第一旅（中文數字）、1（冇區名）、第1旅（冇區名）、港島1（冇「第」同「旅」）" sqref="B3:B500"/>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
@@ -3574,7 +4091,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -3640,44 +4157,32 @@
         <v>119</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>120</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B9" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="C10" s="7" t="s">
+    </row>
+    <row r="11" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="B11" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="D11" s="7" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="E11" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="F11" s="7" t="s">
         <v>127</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -3685,19 +4190,19 @@
         <v>128</v>
       </c>
       <c r="B12" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>129</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -3705,55 +4210,75 @@
         <v>130</v>
       </c>
       <c r="B13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D13" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>132</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" t="s">
+        <v>129</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>136</v>
+      </c>
+      <c r="B15" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C15" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D14" t="s">
-        <v>127</v>
-      </c>
-      <c r="E14" t="s">
-        <v>133</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>134</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>135</v>
+      <c r="D15" t="s">
+        <v>129</v>
+      </c>
+      <c r="E15" t="s">
+        <v>137</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>137</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>140</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
